--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,6 +3876,508 @@
       </c>
       <c r="F145" t="inlineStr"/>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:27:02</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:27:05</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:27:35</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="E148" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:28:04</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:28:12</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:28:26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:28:37</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:28:45</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:30:40</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E154" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:33:22</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>162.41</v>
+      </c>
+      <c r="E155" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:35:29</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>126.87</v>
+      </c>
+      <c r="E156" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:36:12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="E157" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:36:23</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="E158" t="n">
+        <v>53</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:36:49</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="E159" t="n">
+        <v>75</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11</v>
+      </c>
+      <c r="E160" t="n">
+        <v>35</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:07</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="E161" t="n">
+        <v>71</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:11</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="E162" t="n">
+        <v>7</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E163" t="n">
+        <v>7</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E164" t="n">
+        <v>10</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-24 05:37:17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E166" t="n">
+        <v>9</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4378,6 +4378,508 @@
       </c>
       <c r="F166" t="inlineStr"/>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:23:57</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>168.32</v>
+      </c>
+      <c r="E167" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:24:01</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:24:31</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:25:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="E170" t="n">
+        <v>4</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:25:09</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:25:23</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:25:35</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:25:43</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="E174" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:27:42</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="E175" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:30:30</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>167.88</v>
+      </c>
+      <c r="E176" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:32:41</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>130.71</v>
+      </c>
+      <c r="E177" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:33:25</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:33:37</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="E179" t="n">
+        <v>53</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="E180" t="n">
+        <v>75</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="E181" t="n">
+        <v>36</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="E182" t="n">
+        <v>72</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E183" t="n">
+        <v>7</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:27</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E184" t="n">
+        <v>7</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:27</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:29</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E186" t="n">
+        <v>11</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-25 14:34:32</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E187" t="n">
+        <v>9</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4880,6 +4880,508 @@
       </c>
       <c r="F187" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:14:46</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>146.37</v>
+      </c>
+      <c r="E188" t="n">
+        <v>4</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:14:49</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:15:18</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:15:47</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="E191" t="n">
+        <v>4</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:15:55</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:16:07</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:16:17</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:16:24</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:18:01</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="E196" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:20:20</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>139.27</v>
+      </c>
+      <c r="E197" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:22:08</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>107.82</v>
+      </c>
+      <c r="E198" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:22:44</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:22:56</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="E200" t="n">
+        <v>53</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:22</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="E201" t="n">
+        <v>75</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:33</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="E202" t="n">
+        <v>37</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:40</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E203" t="n">
+        <v>70</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:44</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E204" t="n">
+        <v>7</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:44</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E205" t="n">
+        <v>7</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:45</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E206" t="n">
+        <v>10</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:47</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E207" t="n">
+        <v>11</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:23:49</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E208" t="n">
+        <v>9</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5382,6 +5382,508 @@
       </c>
       <c r="F208" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:48:16</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>167.54</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:48:19</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:48:50</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="E211" t="n">
+        <v>5</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:49:19</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:49:28</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:49:42</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:49:53</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:50:01</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:51:59</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="E217" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:54:44</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="E218" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:56:52</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>127.87</v>
+      </c>
+      <c r="E219" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:36</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="E220" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:48</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E221" t="n">
+        <v>55</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:13</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="E222" t="n">
+        <v>75</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="E223" t="n">
+        <v>37</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:31</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E224" t="n">
+        <v>74</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:36</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E225" t="n">
+        <v>7</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:36</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E226" t="n">
+        <v>7</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:37</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E227" t="n">
+        <v>10</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:39</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E228" t="n">
+        <v>11</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:58:41</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E229" t="n">
+        <v>9</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5884,6 +5884,508 @@
       </c>
       <c r="F229" t="inlineStr"/>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:46:31</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>180.08</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:46:34</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:03</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="E232" t="n">
+        <v>5</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:35</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:42</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:47:53</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:48:02</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:48:08</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E237" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:49:32</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>83.59</v>
+      </c>
+      <c r="E238" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:51:31</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="E239" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:53:02</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="E240" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:53:33</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="E241" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:53:44</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="E242" t="n">
+        <v>55</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="E243" t="n">
+        <v>93</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:30</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E244" t="n">
+        <v>37</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:36</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="E245" t="n">
+        <v>74</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:40</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E246" t="n">
+        <v>7</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:41</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E247" t="n">
+        <v>7</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:41</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E248" t="n">
+        <v>10</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:43</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E249" t="n">
+        <v>11</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:46</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E250" t="n">
+        <v>9</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6386,6 +6386,508 @@
       </c>
       <c r="F250" t="inlineStr"/>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:12:20</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>165.46</v>
+      </c>
+      <c r="E251" t="n">
+        <v>4</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:12:23</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:12:54</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E253" t="n">
+        <v>5</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:13:28</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="E254" t="n">
+        <v>4</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:13:36</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:13:50</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E256" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:14:01</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="E257" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:14:09</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E258" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:16:04</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:18:48</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>163.93</v>
+      </c>
+      <c r="E260" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:20:55</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>127.02</v>
+      </c>
+      <c r="E261" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:21:38</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:21:50</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E263" t="n">
+        <v>55</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:24</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="E264" t="n">
+        <v>89</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:35</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="E265" t="n">
+        <v>39</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:42</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="E266" t="n">
+        <v>73</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:47</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E267" t="n">
+        <v>7</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:47</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E268" t="n">
+        <v>7</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:47</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E269" t="n">
+        <v>10</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:50</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E270" t="n">
+        <v>11</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:22:52</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E271" t="n">
+        <v>9</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/logs/daily_lottery_cycle_log.xlsx
+++ b/data/logs/daily_lottery_cycle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:F293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6888,6 +6888,532 @@
       </c>
       <c r="F271" t="inlineStr"/>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:42:04</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Incremental Historical Lottery Update</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="E272" t="n">
+        <v>4</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:42:07</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Run Data Quality Checks</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:42:35</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Export Lottery Features</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="E274" t="n">
+        <v>5</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:43:08</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Generate Base Predictions</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="E275" t="n">
+        <v>4</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:43:14</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Backtest PowerBall Model</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="E276" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:43:25</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Backtest Lotto Model</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="E277" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:43:33</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Backtest Daily Lotto Model</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="E278" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:43:40</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Backtest UK49s Model</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="E279" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:45:01</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Compare PowerBall Models</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="E280" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:46:59</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Compare Lotto Models</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>117.57</v>
+      </c>
+      <c r="E281" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:48:29</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Compare Daily Lotto Models</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>89.93000000000001</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:49:00</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Compare UK49s Models</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="E283" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:49:12</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Run PowerBall Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E284" t="n">
+        <v>55</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:49:46</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Run Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="E285" t="n">
+        <v>89</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:49:57</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Run Daily Lotto Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="E286" t="n">
+        <v>39</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:03</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Run UK49s Genetic Optimizer</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E287" t="n">
+        <v>73</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:04</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Run Adaptive Weight Tuner</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E288" t="n">
+        <v>4</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:08</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Generate PowerBall Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="E289" t="n">
+        <v>7</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:08</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Generate Unified Model Performance Dashboard</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E290" t="n">
+        <v>7</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:09</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Generate Final Ensemble Predictions</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E291" t="n">
+        <v>10</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:11</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Generate Executive Report</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E292" t="n">
+        <v>11</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-28 19:50:13</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Generate Daily Summary</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E293" t="n">
+        <v>9</v>
+      </c>
+      <c r="F293" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
